--- a/ExportExcel/Sorter Product Tests.xlsx
+++ b/ExportExcel/Sorter Product Tests.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="13">
   <si>
     <t>STT</t>
   </si>
@@ -38,10 +38,19 @@
     <t/>
   </si>
   <si>
-    <t>SKIPPED</t>
-  </si>
-  <si>
-    <t>0 ms</t>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>1077 ms</t>
+  </si>
+  <si>
+    <t>1081 ms</t>
+  </si>
+  <si>
+    <t>1086 ms</t>
+  </si>
+  <si>
+    <t>1090 ms</t>
   </si>
 </sst>
 </file>
@@ -114,7 +123,7 @@
     <col min="1" max="1" width="3.76171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="21.6171875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.52734375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="7.57421875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="7.08203125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="13.2109375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="18.703125" customWidth="true" bestFit="true"/>
   </cols>
@@ -149,7 +158,7 @@
       <c r="C2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E2" t="s" s="0">
@@ -169,11 +178,11 @@
       <c r="C3" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>7</v>
@@ -189,11 +198,11 @@
       <c r="C4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D4" t="s" s="0">
+      <c r="D4" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>7</v>
@@ -209,11 +218,11 @@
       <c r="C5" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D5" t="s" s="0">
+      <c r="D5" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>7</v>
